--- a/results/Int Task Remove ACC -0.0/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_8_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7625216087647395</v>
+        <v>0.7609343467729665</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7579790909476425</v>
+        <v>0.7433719401614951</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7587037485126435</v>
+        <v>0.7316534415621672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7419732637529031</v>
+        <v>0.7301018511820274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7434584999463678</v>
+        <v>0.7133559004088516</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7418405553795535</v>
+        <v>0.7133559004088516</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7425702019811464</v>
+        <v>0.7323576440771404</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7374407240089902</v>
+        <v>0.7342971320523151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7326839270702631</v>
+        <v>0.7218639539611703</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7409572464509241</v>
+        <v>0.7339653611189412</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7396710728174836</v>
+        <v>0.7331895659288713</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.735812551917162</v>
+        <v>0.7326894150105143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7319081318801932</v>
+        <v>0.7398194966560983</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7267634373464312</v>
+        <v>0.7412486061879021</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7254670361879769</v>
+        <v>0.7567694990258906</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7254670361879769</v>
+        <v>0.7567694990258906</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7263755397513963</v>
+        <v>0.7577443567759847</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7200007982458547</v>
+        <v>0.7511603251854051</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7277689776715668</v>
+        <v>0.7523240179705097</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7249209861329728</v>
+        <v>0.7502924822702113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.727758750146553</v>
+        <v>0.7374971001224808</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6921435146266079</v>
+        <v>0.7383290219742117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6921435146266079</v>
+        <v>0.7423150127594611</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6880704651528267</v>
+        <v>0.7461174069981216</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6880704651528267</v>
+        <v>0.7350265292020784</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6880704651528267</v>
+        <v>0.7320356017651212</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6974563396935234</v>
+        <v>0.7112724787279953</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6896881602678115</v>
+        <v>0.7301213084247367</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7068936013111188</v>
+        <v>0.724129475477638</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7053674550175988</v>
+        <v>0.7233536802875681</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.723460944574298</v>
+        <v>0.7233536802875681</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7340564110367467</v>
+        <v>0.7206281695973099</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6923420782829732</v>
+        <v>0.7200005487940251</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6949910072615428</v>
+        <v>0.685845354832755</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6914131196695262</v>
+        <v>0.6968494233920959</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6706707011342574</v>
+        <v>0.6909239446316719</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6620910549068422</v>
+        <v>0.6841715330561092</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6916121822295506</v>
+        <v>0.6611733216257274</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6911579304478408</v>
+        <v>0.6496895571980572</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6842982545855483</v>
+        <v>0.6432586890308547</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7068629187360775</v>
+        <v>0.6544463541367844</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7034688771424794</v>
+        <v>0.6473419660296498</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.661795454488761</v>
+        <v>0.6828190052359939</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6675423257391881</v>
+        <v>0.6907707812082948</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6671544281441533</v>
+        <v>0.6775261363154468</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7034279670424243</v>
+        <v>0.6953437321486035</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6885499115693264</v>
+        <v>0.6953437321486035</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.669364321902619</v>
+        <v>0.7028305299105216</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6445286482953709</v>
+        <v>0.7060255089440954</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6534552820177659</v>
+        <v>0.7033104752306806</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6508472631392515</v>
+        <v>0.6824760089702877</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6457841393537701</v>
+        <v>0.700033426545167</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6418388092167462</v>
+        <v>0.7002324891051913</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.638347730861432</v>
+        <v>0.6711711015044439</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6387254009314531</v>
+        <v>0.672977881106269</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6541544954961471</v>
+        <v>0.6746928624347995</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.605115758121528</v>
+        <v>0.68122600585214</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6331616273239556</v>
+        <v>0.6987068417153306</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.63378949757907</v>
+        <v>0.7157434038699957</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6201217823832129</v>
+        <v>0.7185811678835758</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6201212834795538</v>
+        <v>0.6705833929938959</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6193352607644701</v>
+        <v>0.6122301243018466</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6214738112996689</v>
+        <v>0.6074274282264723</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6172273928043125</v>
+        <v>0.6100100030183672</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5746806392951489</v>
+        <v>0.6100100030183672</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5679077726695587</v>
+        <v>0.5919574235617231</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5654783613010409</v>
+        <v>0.5318230688062981</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5080745062724662</v>
+        <v>0.517343138453249</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5080745062724662</v>
+        <v>0.5054305663304888</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5080745062724662</v>
+        <v>0.5015515903801396</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5069771676740363</v>
+        <v>0.5019394879751745</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5055480581422325</v>
+        <v>0.5019394879751745</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5041648477470758</v>
+        <v>0.5019394879751745</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4990303807383276</v>
+        <v>0.5023273855702095</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4984586371448742</v>
+        <v>0.5019394879751745</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4962078332863533</v>
+        <v>0.5019394879751745</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5019394879751745</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.5015515903801396</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.5015515903801396</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.5015515903801396</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.5011636927851048</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.5011636927851048</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.5011636927851048</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.5011636927851048</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5003878975950349</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5000663541866748</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5004542517817098</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5000663541866748</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.5003878975950349</v>
       </c>
     </row>
   </sheetData>
